--- a/agenda/data/schedule.xlsx
+++ b/agenda/data/schedule.xlsx
@@ -19,7 +19,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9.5"/>
+        <sz val="9.0"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
         <family val="1"/>
@@ -31,7 +31,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9.5"/>
+        <sz val="9.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -42,7 +42,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -53,7 +53,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -64,7 +64,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -75,7 +75,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -86,7 +86,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -97,18 +97,18 @@
     <r>
       <rPr>
         <b/>
-        <sz val="6.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">HAM - PALESTRA</t>
+        <sz val="6.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">HAM - PRÁTICA</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="6.5"/>
+        <sz val="6.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -119,7 +119,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
@@ -131,7 +131,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="6.5"/>
+        <sz val="6.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -141,17 +141,27 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">08:00 - 08:50                                    TODOS - Prof. Michel Batista</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">09:00 - 10:40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">GRUPO 1 - Michel Batista</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
@@ -161,7 +171,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -171,7 +181,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -181,7 +191,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -191,8 +201,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
-        <color rgb="FF232323"/>
+        <sz val="4.5"/>
+        <color rgb="FF222222"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
@@ -202,7 +212,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -212,69 +222,49 @@
   <si>
     <r>
       <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Roberta Mota - 5/6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Luane Costa - 3/4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Adriano Monteiro - 5/6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b/>
-        <sz val="6.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">HAM - PRÁTICA</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">09:00 - 10:40</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">GRUPO 1 - Michel Batista</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Roberta Mota - 5/6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Luane Costa - 3/4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Adriano Monteiro - 5/6</t>
+        <sz val="6.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">CI PRATICA - POLICLÍNICA REGIONAL</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="6.5"/>
+        <sz val="6.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -284,7 +274,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
@@ -294,7 +284,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -304,7 +294,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -314,7 +304,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -324,7 +314,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -334,7 +324,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -344,7 +334,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -354,18 +344,18 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Daniela Leão - 5/6</t>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Daniela Leão - 8/7</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="6.5"/>
+        <sz val="6.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -375,7 +365,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="5.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -385,7 +375,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
@@ -395,7 +385,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="5.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -405,7 +395,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
@@ -415,7 +405,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="5.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -425,7 +415,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
@@ -435,7 +425,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
@@ -446,7 +436,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9.5"/>
+        <sz val="9.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -456,7 +446,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -466,7 +456,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -476,7 +466,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
@@ -486,7 +476,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -496,7 +486,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -506,7 +496,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -516,7 +506,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
@@ -526,7 +516,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -536,8 +526,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
-        <color rgb="FF232323"/>
+        <sz val="4.5"/>
+        <color rgb="FF222222"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
@@ -547,7 +537,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -558,7 +548,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="6.5"/>
+        <sz val="6.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -568,17 +558,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Daniela Leão -  7/8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -588,7 +568,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -598,7 +578,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -608,7 +588,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -618,17 +598,27 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Grupo 02  - Profa. Agnis de Jesus</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Grupo 01  - Profa. Agnis de Jesus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Daniela Leão -  5/6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -638,7 +628,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -649,7 +639,18 @@
     <r>
       <rPr>
         <b/>
-        <sz val="6.5"/>
+        <sz val="6.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">CI PRATICA - Casa da Criança</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="6.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -659,47 +660,38 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">18:00 - 19:05</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+        <b/>
+        <sz val="6.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">HAM - PALESTRA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Prof. Adriano Monteiro, Profa Naira e
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+      <t xml:space="preserve">Karla Baleeiro - 1/2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Prof. Iomar</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="6.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">CI PRATICA - Casa da Criança</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+      <t xml:space="preserve">Christielle - 7/8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -709,183 +701,263 @@
   <si>
     <r>
       <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Grupo 03  - Profa. Agnis de Jesus</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">19:25 - 20:25</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="6.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">MOMENTO NED (mensal)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Grupo 02  - Profa. Agnis de Jesus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:00 - 16:05</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Karla Baleeiro - 1/2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+      <t xml:space="preserve">Prof. Adriano Monteiro</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">18:0 - 18:50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">TODOS - Prof. Michel Batista</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:25 - 17:25</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="6.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">CLÍNICA INTEGRADA - CI - PALESTRA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="6.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">MOMENTO NED (mensal)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="6.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">IESC - PALESTRA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">17:30 - 18:20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Christielle - 7/8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="6.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">CLÍNICA INTEGRADA - CI - PALESTRA</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">20:00 - 20:50</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Grupo 04  - Profa. Agnis de Jesus</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">20:30 - 21:20</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+      <t xml:space="preserve">Prof. Adriano Monteiro, Profa. Naira e Prof. Iomar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">18:00 - 19:05</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Prof. Adriano Monteiro, Profa Naira e Prof. Iomar</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+      <t xml:space="preserve">Prof. Adriano Monteiro, Profa Naira
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Prof. Marcelo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="6.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">IESC - PALESTRA</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+      <t xml:space="preserve">e Prof. Iomar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">18:30 - 20:10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Profa. Agnis de Jesus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:00 - 20:50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Grupo 03 - Profa. Agnis de Jesus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">19:25 - 20:25</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:30 - 21:20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Prof. Adriano Monteiro, Profa
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
+      <t xml:space="preserve">Prof. Marcelo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">18:20 - 19:25</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Naira e Prof. Iomar</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">18:30 - 20:10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Profa. Agnis de Jesus</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">20:10 - 21:00</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Grupo 01  - Profa. Agnis de Jesus</t>
+      <t xml:space="preserve">Profa. Naira e Prof. Iomar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">21:00 - 21:50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Grupo 04  - Profa. Agnis de Jesus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">19:45 - 20:25</t>
     </r>
   </si>
 </sst>
@@ -894,7 +966,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -903,31 +975,35 @@
     </font>
     <font>
       <b/>
-      <sz val="9.5"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="5.5"/>
+      <sz val="4.5"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="6.5"/>
+      <sz val="6"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="5.5"/>
+      <sz val="4.5"/>
       <name val="Trebuchet MS"/>
     </font>
     <font>
-      <sz val="5.5"/>
+      <sz val="4.5"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="5.5"/>
+      <sz val="4.5"/>
       <name val="Trebuchet MS"/>
+    </font>
+    <font>
+      <sz val="5"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="11">
@@ -944,12 +1020,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE1EED9"/>
+        <fgColor rgb="FFE0EDD9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD76CCD"/>
+        <fgColor rgb="FFD66CCD"/>
       </patternFill>
     </fill>
     <fill>
@@ -959,7 +1035,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4EA72D"/>
+        <fgColor rgb="FF4EA72C"/>
       </patternFill>
     </fill>
     <fill>
@@ -979,11 +1055,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0A983"/>
+        <fgColor rgb="FFEFA983"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1151,20 +1227,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="159">
     <xf numFmtId="0" fillId="0" borderId="0" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1241,27 +1308,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="5" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="4" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="3" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="5" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1271,37 +1317,190 @@
       <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="4" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="1" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="5" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="6" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="7" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="8" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="9" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="10" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="7" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="7" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="7" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="7" borderId="1" fontId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="7" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="4" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="4" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fillId="4" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="4" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="4" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="4" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="5" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
@@ -1312,13 +1511,16 @@
     <xf numFmtId="0" fillId="5" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fillId="9" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fillId="9" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fillId="9" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="12" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1327,227 +1529,56 @@
     <xf numFmtId="0" fillId="5" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fillId="5" borderId="12" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fillId="5" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="12" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fillId="5" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fillId="5" borderId="12" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="4" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="6" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="8" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="10" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="5" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="14" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="7" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="0" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="7" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="7" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="7" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="7" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="7" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="3" borderId="13" fontId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="3" borderId="9" fontId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="3" borderId="15" fontId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="3" borderId="10" fontId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fillId="5" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="12" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="8" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="8" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fillId="8" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="8" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
+    <xf numFmtId="0" fillId="9" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="4" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="4" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="4" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="9" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
@@ -1558,71 +1589,38 @@
     <xf numFmtId="0" fillId="9" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fillId="10" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="10" borderId="5" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="10" borderId="6" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="10" borderId="9" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="10" borderId="10" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fillId="9" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="9" borderId="1" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="10" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="7" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="10" borderId="5" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="7" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="10" borderId="6" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="7" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="10" borderId="9" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="7" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="10" borderId="10" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="7" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="12" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="12" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="12" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="9" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="9" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="9" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="9" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="9" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="9" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="9" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1633,14 +1631,41 @@
     <xf numFmtId="0" fillId="9" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fillId="9" borderId="1" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fillId="9" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="9" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="9" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="9" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
@@ -1648,56 +1673,41 @@
     <xf numFmtId="0" fillId="9" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fillId="9" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fillId="9" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="9" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fillId="9" borderId="11" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fillId="9" borderId="12" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fillId="9" borderId="13" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="9" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="9" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="9" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="6" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="6" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="6" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="6" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="8" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fillId="9" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="9" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="11" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="13" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="5" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="14" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1993,22 +2003,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="11.333333"/>
-    <col min="2" max="2" customWidth="1" width="30.888889"/>
-    <col min="3" max="3" customWidth="1" width="16.666667"/>
-    <col min="4" max="4" customWidth="1" width="17.555556"/>
-    <col min="5" max="5" customWidth="1" width="8.888889"/>
-    <col min="6" max="6" customWidth="1" width="22.666667"/>
-    <col min="7" max="7" customWidth="1" width="7.777778"/>
-    <col min="8" max="8" customWidth="1" width="26"/>
-    <col min="9" max="9" customWidth="1" width="8.222222"/>
-    <col min="10" max="10" customWidth="1" width="20.444444"/>
+    <col min="1" max="1" customWidth="1" width="12.222222"/>
+    <col min="2" max="2" customWidth="1" width="30"/>
+    <col min="3" max="3" customWidth="1" width="17.777778"/>
+    <col min="4" max="4" customWidth="1" width="19.333333"/>
+    <col min="5" max="5" customWidth="1" width="10"/>
+    <col min="6" max="6" customWidth="1" width="24.444444"/>
+    <col min="7" max="7" customWidth="1" width="8.666667"/>
+    <col min="8" max="8" customWidth="1" width="28.222222"/>
+    <col min="9" max="9" customWidth="1" width="8.888889"/>
+    <col min="10" max="10" customWidth="1" width="26.666667"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.75" customHeight="1">
+    <row r="1" spans="1:10" ht="13.50" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2022,7 +2032,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="4"/>
     </row>
-    <row r="2" spans="1:10" ht="14.25" customHeight="1">
+    <row r="2" spans="1:10" ht="13.50" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -2036,7 +2046,7 @@
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
     </row>
-    <row r="3" spans="1:10" ht="8.25" customHeight="1">
+    <row r="3" spans="1:10" ht="7.50" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -2058,7 +2068,7 @@
       </c>
       <c r="J3" s="11"/>
     </row>
-    <row r="4" spans="1:10" ht="9.00" customHeight="1">
+    <row r="4" spans="1:10" ht="8.25" customHeight="1">
       <c r="A4" s="13" t="s">
         <v>7</v>
       </c>
@@ -2080,37 +2090,37 @@
       </c>
       <c r="J4" s="27"/>
     </row>
-    <row r="5" spans="1:10" ht="14.75" customHeight="1">
+    <row r="5" spans="1:10" ht="13.25" customHeight="1">
       <c r="A5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="30" t="s">
+      <c r="B5" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="C5" s="36" t="s">
         <v>13</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>14</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="22"/>
-      <c r="G5" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="31" t="s">
+      <c r="G5" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="30" t="s">
+      <c r="H5" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="31" t="s">
+      <c r="I5" s="36" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="9.25" customHeight="1">
-      <c r="A6" s="13" t="s">
+      <c r="J5" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="14"/>
+    </row>
+    <row r="6" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A6" s="30"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="16" t="s">
         <v>8</v>
       </c>
@@ -2121,531 +2131,523 @@
         <v>8</v>
       </c>
       <c r="H6" s="17"/>
-      <c r="I6" s="33" t="s">
+      <c r="I6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="34"/>
-    </row>
-    <row r="7" spans="1:10" ht="14.75" customHeight="1">
-      <c r="A7" s="36" t="s">
+      <c r="J6" s="17"/>
+    </row>
+    <row r="7" spans="1:10" ht="13.25" customHeight="1">
+      <c r="A7" s="30"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="37" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>21</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="22"/>
-      <c r="G7" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="9.25" customHeight="1">
-      <c r="A8" s="37"/>
-      <c r="B8" s="41"/>
+      <c r="G7" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A8" s="30"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="16" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="21"/>
       <c r="F8" s="22"/>
-      <c r="G8" s="44" t="s">
+      <c r="G8" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="27"/>
+      <c r="I8" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="40"/>
+    </row>
+    <row r="9" spans="1:10" ht="13.25" customHeight="1">
+      <c r="A9" s="31"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="36" t="s">
         <v>24</v>
-      </c>
-      <c r="H8" s="45"/>
-      <c r="I8" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="48"/>
-    </row>
-    <row r="9" spans="1:10" ht="7.50" customHeight="1">
-      <c r="A9" s="38"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>25</v>
       </c>
       <c r="E9" s="21"/>
       <c r="F9" s="22"/>
-      <c r="G9" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="59" t="s">
+      <c r="G9" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="56" t="s">
+      <c r="J9" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="62" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="9.25" customHeight="1">
+    </row>
+    <row r="10" spans="1:10" ht="8.25" customHeight="1">
       <c r="A10" s="13" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B10" s="14"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="54"/>
+      <c r="C10" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="40"/>
       <c r="E10" s="21"/>
       <c r="F10" s="22"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="63"/>
-    </row>
-    <row r="11" spans="1:10" ht="9.25" customHeight="1">
-      <c r="A11" s="65" t="s">
+      <c r="G10" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
+    </row>
+    <row r="11" spans="1:10" ht="13.25" customHeight="1">
+      <c r="A11" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="C11" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="45"/>
       <c r="E11" s="21"/>
       <c r="F11" s="22"/>
-      <c r="G11" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="73"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.00" customHeight="1">
-      <c r="A12" s="66"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="31" t="s">
+      <c r="G11" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="37" t="s">
         <v>31</v>
       </c>
+      <c r="I11" s="44"/>
+      <c r="J11" s="45"/>
+    </row>
+    <row r="12" spans="1:10" ht="8.50" customHeight="1">
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="50"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="31" t="s">
+      <c r="G12" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="74"/>
-      <c r="J12" s="75"/>
-    </row>
-    <row r="13" spans="1:10" ht="9.00" customHeight="1">
-      <c r="A13" s="66"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="77" t="s">
+      <c r="H12" s="50"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="45"/>
+    </row>
+    <row r="13" spans="1:10" ht="13.25" customHeight="1">
+      <c r="A13" s="30"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="78"/>
+      <c r="D13" s="52" t="s">
+        <v>34</v>
+      </c>
       <c r="E13" s="21"/>
       <c r="F13" s="22"/>
-      <c r="G13" s="77" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="78"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="75"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.75" customHeight="1">
-      <c r="A14" s="66"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="79" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="80" t="s">
+      <c r="G13" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="79" t="s">
+      <c r="H13" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="80" t="s">
+      <c r="I13" s="44"/>
+      <c r="J13" s="45"/>
+    </row>
+    <row r="14" spans="1:10" ht="13.25" customHeight="1">
+      <c r="A14" s="31"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="I14" s="74"/>
-      <c r="J14" s="75"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.25" customHeight="1">
-      <c r="A15" s="67"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="79" t="s">
+      <c r="D14" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="80" t="s">
+      <c r="E14" s="23"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="79" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="80" t="s">
+      <c r="I14" s="46"/>
+      <c r="J14" s="47"/>
+    </row>
+    <row r="15" spans="1:10" ht="13.50" customHeight="1">
+      <c r="A15" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="74"/>
-      <c r="J15" s="75"/>
-    </row>
-    <row r="16" spans="1:10" ht="14.75" customHeight="1">
-      <c r="A16" s="82" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A16" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="27"/>
+      <c r="G16" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="40"/>
+      <c r="I16" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="40"/>
+    </row>
+    <row r="17" spans="1:10" ht="20.25" customHeight="1">
+      <c r="A17" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="83"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="84"/>
-    </row>
-    <row r="17" spans="1:10" ht="9.25" customHeight="1">
-      <c r="A17" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="16" t="s">
+      <c r="B17" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="54" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A18" s="31"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="40"/>
+      <c r="E18" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="33" t="s">
+      <c r="F18" s="27"/>
+      <c r="G18" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="59"/>
+      <c r="I18" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="45"/>
-      <c r="I17" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="48"/>
-    </row>
-    <row r="18" spans="1:10" ht="14.75" customHeight="1">
-      <c r="A18" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="40" t="s">
+      <c r="J18" s="17"/>
+    </row>
+    <row r="19" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A19" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="86" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="89" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="92" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="95" t="s">
+      <c r="D19" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="67" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="73" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="76" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="98" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="101" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="31" t="s">
+      <c r="J19" s="82" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="13.25" customHeight="1">
+      <c r="A20" s="85" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="62"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="83"/>
+    </row>
+    <row r="21" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A21" s="86"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="91" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="92"/>
+      <c r="E21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="58" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="9.25" customHeight="1">
-      <c r="A19" s="37"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="96"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="102"/>
-      <c r="I19" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="34"/>
-    </row>
-    <row r="20" spans="1:10" ht="9.25" customHeight="1">
-      <c r="A20" s="38"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="45"/>
-      <c r="E20" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="34"/>
-      <c r="G20" s="104" t="s">
-        <v>52</v>
-      </c>
-      <c r="H20" s="105"/>
-      <c r="I20" s="107" t="s">
-        <v>48</v>
-      </c>
-      <c r="J20" s="62" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="9.25" customHeight="1">
-      <c r="A21" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21" s="117" t="s">
-        <v>57</v>
-      </c>
-      <c r="H21" s="121" t="s">
-        <v>58</v>
-      </c>
-      <c r="I21" s="108"/>
-      <c r="J21" s="63"/>
-    </row>
-    <row r="22" spans="1:10" ht="9.25" customHeight="1">
-      <c r="A22" s="125" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="69" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="109"/>
-      <c r="D22" s="112"/>
-      <c r="E22" s="114"/>
-      <c r="F22" s="115"/>
-      <c r="G22" s="118"/>
-      <c r="H22" s="122"/>
-      <c r="I22" s="129" t="s">
+      <c r="H21" s="59"/>
+      <c r="I21" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="J22" s="130"/>
-    </row>
-    <row r="23" spans="1:10" ht="16.50" customHeight="1">
-      <c r="A23" s="126"/>
-      <c r="B23" s="70"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="113"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="123"/>
-      <c r="I23" s="131" t="s">
+      <c r="J21" s="95"/>
+    </row>
+    <row r="22" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A22" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="J23" s="132" t="s">
+      <c r="B22" s="14"/>
+      <c r="C22" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="98" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="16.50" customHeight="1">
-      <c r="A24" s="127"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="47" t="s">
+      <c r="E22" s="102" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="48"/>
-      <c r="E24" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="117" t="s">
+      <c r="G22" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="H24" s="121" t="s">
+      <c r="H22" s="76" t="s">
         <v>66</v>
       </c>
-      <c r="I24" s="131" t="s">
+      <c r="I22" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="J24" s="132" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="9.25" customHeight="1">
-      <c r="A25" s="134" t="s">
+      <c r="J22" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="135"/>
-      <c r="C25" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="53" t="s">
+    </row>
+    <row r="23" spans="1:10" ht="7.50" customHeight="1">
+      <c r="A23" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="140" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="144" t="s">
+      <c r="B23" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="119"/>
-      <c r="H25" s="123"/>
-      <c r="I25" s="148" t="s">
+      <c r="C23" s="96"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="109"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="111" t="s">
         <v>71</v>
       </c>
-      <c r="J25" s="149"/>
-    </row>
-    <row r="26" spans="1:10" ht="7.50" customHeight="1">
-      <c r="A26" s="136"/>
-      <c r="B26" s="137"/>
-      <c r="C26" s="109"/>
-      <c r="D26" s="138"/>
-      <c r="E26" s="141"/>
-      <c r="F26" s="145"/>
-      <c r="G26" s="117" t="s">
+      <c r="J23" s="112" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A24" s="86"/>
+      <c r="B24" s="115"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="100"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="108"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="H26" s="121" t="s">
+      <c r="J24" s="118"/>
+    </row>
+    <row r="25" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A25" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="151" t="s">
+      <c r="B25" s="121"/>
+      <c r="C25" s="94" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="95"/>
+      <c r="E25" s="125" t="s">
         <v>74</v>
       </c>
-      <c r="J26" s="154" t="s">
+      <c r="F25" s="126"/>
+      <c r="G25" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="H25" s="59"/>
+      <c r="I25" s="128" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="13.50" customHeight="1">
-      <c r="A27" s="157" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="158"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="146"/>
-      <c r="G27" s="119"/>
-      <c r="H27" s="123"/>
-      <c r="I27" s="152"/>
-      <c r="J27" s="155"/>
-    </row>
-    <row r="28" spans="1:10" ht="9.25" customHeight="1">
-      <c r="A28" s="160" t="s">
-        <v>74</v>
-      </c>
-      <c r="B28" s="163" t="s">
+      <c r="J25" s="131" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="166" t="s">
+    </row>
+    <row r="26" spans="1:10" ht="15.00" customHeight="1">
+      <c r="A26" s="122"/>
+      <c r="B26" s="123"/>
+      <c r="C26" s="111" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="135" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="139" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="76" t="s">
+        <v>82</v>
+      </c>
+      <c r="I26" s="129"/>
+      <c r="J26" s="132"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.00" customHeight="1">
+      <c r="A27" s="143" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="144"/>
+      <c r="C27" s="111" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="136"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="167"/>
-      <c r="E28" s="169" t="s">
-        <v>77</v>
-      </c>
-      <c r="F28" s="170"/>
-      <c r="G28" s="104" t="s">
-        <v>52</v>
-      </c>
-      <c r="H28" s="105"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="73"/>
-    </row>
-    <row r="29" spans="1:10" ht="16.50" customHeight="1">
-      <c r="A29" s="161"/>
-      <c r="B29" s="164"/>
-      <c r="C29" s="131" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" s="132" t="s">
+      <c r="J27" s="95"/>
+    </row>
+    <row r="28" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A28" s="146" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="149" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="94" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="95"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28" s="59"/>
+      <c r="I28" s="111" t="s">
+        <v>86</v>
+      </c>
+      <c r="J28" s="112" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A29" s="147"/>
+      <c r="B29" s="150"/>
+      <c r="C29" s="153" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="155" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="117" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" s="172" t="s">
-        <v>80</v>
-      </c>
-      <c r="G29" s="117" t="s">
-        <v>81</v>
-      </c>
-      <c r="H29" s="121" t="s">
-        <v>82</v>
-      </c>
-      <c r="I29" s="74"/>
-      <c r="J29" s="75"/>
-    </row>
-    <row r="30" spans="1:10" ht="16.50" customHeight="1">
-      <c r="A30" s="73"/>
-      <c r="B30" s="174"/>
-      <c r="C30" s="131" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="132" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" s="119"/>
-      <c r="F30" s="173"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="123"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="75"/>
-    </row>
-    <row r="31" spans="1:10" ht="9.25" customHeight="1">
-      <c r="A31" s="75"/>
-      <c r="B31" s="175"/>
-      <c r="C31" s="166" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="167"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-    </row>
-    <row r="32" spans="1:10" ht="21.25" customHeight="1">
-      <c r="A32" s="75"/>
-      <c r="B32" s="175"/>
-      <c r="C32" s="176" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="177" t="s">
-        <v>75</v>
-      </c>
-      <c r="E32" s="74"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
+      <c r="E29" s="136"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="I29" s="111" t="s">
+        <v>90</v>
+      </c>
+      <c r="J29" s="112" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="6.50" customHeight="1">
+      <c r="A30" s="148"/>
+      <c r="B30" s="151"/>
+      <c r="C30" s="154"/>
+      <c r="D30" s="156"/>
+      <c r="E30" s="137"/>
+      <c r="F30" s="141"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="157"/>
+      <c r="J30" s="158"/>
     </row>
   </sheetData>
-  <mergeCells count="94">
+  <mergeCells count="86">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:B3"/>
@@ -2655,91 +2657,83 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F15"/>
+    <mergeCell ref="E4:F14"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="B5:B9"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="I6:J6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J15"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J14"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="I24:J24"/>
     <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="E26:E30"/>
+    <mergeCell ref="F26:F30"/>
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
     <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
     <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:J30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
     <mergeCell ref="G29:G30"/>
     <mergeCell ref="H29:H30"/>
-    <mergeCell ref="A30:B32"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:J32"/>
+    <mergeCell ref="I30:J30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
